--- a/02_DIA_inicio_2026_analisis_assets/rbd_9593_escuela-basica-educadores-de-chile_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9593_escuela-basica-educadores-de-chile_nt2_rubricas.xlsx
@@ -1776,13 +1776,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5DE60509-0CF2-4CE2-9DA2-9319A47BD5A6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20DC96A3-D7F2-449D-8B3A-D5FC864FC355}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7FEFE6D1-AA81-4E44-B2F0-1918C70D8F92}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{17CD5131-5814-45A8-B65C-80A1E617A517}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F88C842-E56D-48B8-B950-BD35F4FA3286}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C8E167F-244C-4953-BE35-6BE1C8CB89A8}"/>
 </file>